--- a/samples/converted/03_bank_statement.xlsx
+++ b/samples/converted/03_bank_statement.xlsx
@@ -12,9 +12,11 @@
     <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Corrections" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Page coverage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Run log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Overview'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table 1'!$A$1:$P$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Table 1'!$1:$1</definedName>
@@ -24,6 +26,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Evidence'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Corrections'!$A$1:$F$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Corrections'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Page coverage'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Page coverage'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Run log'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Run log'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -517,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -605,7 +611,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -628,36 +634,106 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LedgerLens 1.0 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>LedgerLens 1.1 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Interpretation</t>
+          <t>Review status</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
+          <t>Draft — review pending</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>Pages with extracted tables</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Validation errors</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Validation warnings</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Rows with source evidence</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Review completed (UTC)</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Pages without extracted tables are explicitly flagged. No guarantee for arbitrary layouts.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2996,4 +3072,320 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Extraction</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Table fragments</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Data rows (page estimate)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Seconds</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Attempts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time (UTC)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.532756+00:00</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>inspect</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Opened source document</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.537161+00:00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>inspect</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Selected native text extraction</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.619635+00:00</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Extracted table fragments</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.622057+00:00</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>inspect</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Selected native text extraction</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.706562+00:00</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Extracted table fragments</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.706562+00:00</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>align</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Matching table schemas and continuation pages</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.707737+00:00</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>validate</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Checking totals, arithmetic, balances and table integrity</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T06:05:51.710740+00:00</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Extraction complete; human review is pending</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/samples/converted/03_bank_statement.xlsx
+++ b/samples/converted/03_bank_statement.xlsx
@@ -912,9 +912,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P2" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="6" t="n">
@@ -980,9 +978,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -1048,9 +1044,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="n">
@@ -1116,9 +1110,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P5" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P5" s="3" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1184,9 +1176,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P6" s="2" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -1250,9 +1240,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P7" s="3" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -1318,9 +1306,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P8" s="2" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -1386,9 +1372,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P9" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P9" s="3" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -1454,9 +1438,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P10" s="2" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -1522,9 +1504,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P11" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P11" s="3" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -1590,9 +1570,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="n">
@@ -1654,9 +1632,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P13" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P13" s="3" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -1722,9 +1698,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P14" s="2" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="n">
@@ -1790,9 +1764,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P15" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P15" s="3" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -1858,9 +1830,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P16" s="2" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="n">
@@ -1926,9 +1896,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P17" s="3" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -1994,9 +1962,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P18" s="2" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="n">
@@ -2062,9 +2028,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P19" s="3" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -2130,9 +2094,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P20" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P20" s="2" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="n">
@@ -2198,9 +2160,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="P21" s="3" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -2234,9 +2194,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="P22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="P22" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P22"/>
@@ -2527,9 +2485,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -2551,9 +2507,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -2575,9 +2529,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -2599,9 +2551,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -2623,9 +2573,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -2647,9 +2595,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -2671,9 +2617,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -2695,9 +2639,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -2719,9 +2661,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -2743,9 +2683,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -2767,9 +2705,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -2791,9 +2727,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -2815,9 +2749,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -2839,9 +2771,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -2863,9 +2793,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -2887,9 +2815,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -2911,9 +2837,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -2935,9 +2859,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -2959,9 +2881,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -2983,9 +2903,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -3007,9 +2925,7 @@
           <t>Native PDF · grid</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="F22" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F22"/>

--- a/samples/converted/03_bank_statement.xlsx
+++ b/samples/converted/03_bank_statement.xlsx
@@ -533,7 +533,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LedgerLens extraction report</t>
+          <t>DamnLens AI Agent extraction report</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>f87639d73f556fd4039fe771246ad338a2e2907187bf587e1f8d3a1fd5b630af</t>
+          <t>53cb667641ff8b00ec81da175a11ff5c046bbe7c5b1820dca7b059ebe1ffd063</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LedgerLens 1.1 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>DamnLens AI Agent 1.2 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.532756+00:00</t>
+          <t>2026-10-15T06:40:06.395638+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.537161+00:00</t>
+          <t>2026-10-15T06:40:06.408130+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.619635+00:00</t>
+          <t>2026-10-15T06:40:06.484141+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.622057+00:00</t>
+          <t>2026-10-15T06:40:06.490079+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3228,7 +3228,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.706562+00:00</t>
+          <t>2026-10-15T06:40:06.570979+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.706562+00:00</t>
+          <t>2026-10-15T06:40:06.570979+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.707737+00:00</t>
+          <t>2026-10-15T06:40:06.570979+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:05:51.710740+00:00</t>
+          <t>2026-10-15T06:40:06.570979+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">

--- a/samples/converted/03_bank_statement.xlsx
+++ b/samples/converted/03_bank_statement.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DamnLens AI Agent 1.2 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>DamnLens AI Agent 1.3 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.395638+00:00</t>
+          <t>2026-10-15T07:48:29.259410+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.408130+00:00</t>
+          <t>2026-10-15T07:48:29.264621+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.484141+00:00</t>
+          <t>2026-10-15T07:48:29.388726+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.490079+00:00</t>
+          <t>2026-10-15T07:48:29.390732+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3228,7 +3228,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.570979+00:00</t>
+          <t>2026-10-15T07:48:29.525677+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.570979+00:00</t>
+          <t>2026-10-15T07:48:29.526635+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.570979+00:00</t>
+          <t>2026-10-15T07:48:29.528856+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T06:40:06.570979+00:00</t>
+          <t>2026-10-15T07:48:29.531685+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">

--- a/samples/converted/03_bank_statement.xlsx
+++ b/samples/converted/03_bank_statement.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -634,7 +634,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>DamnLens AI Agent 1.3 · PyMuPDF + RapidOCR (PP-OCR / ONNX)</t>
+          <t>DamnLens AI Agent 1.4 · PyMuPDF + RapidOCR (PP-OCRv3/v5 / ONNX)</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.259410+00:00</t>
+          <t>2026-10-15T08:42:34.437923+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.264621+00:00</t>
+          <t>2026-10-15T08:42:34.441382+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.388726+00:00</t>
+          <t>2026-10-15T08:42:34.571597+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.390732+00:00</t>
+          <t>2026-10-15T08:42:34.572888+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3228,7 +3228,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.525677+00:00</t>
+          <t>2026-10-15T08:42:34.703749+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.526635+00:00</t>
+          <t>2026-10-15T08:42:34.703749+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.528856+00:00</t>
+          <t>2026-10-15T08:42:34.711915+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T07:48:29.531685+00:00</t>
+          <t>2026-10-15T08:42:34.714419+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">

--- a/samples/converted/03_bank_statement.xlsx
+++ b/samples/converted/03_bank_statement.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Run log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$B$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Overview'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Table 1'!$A$1:$P$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Table 1'!$1:$1</definedName>
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -641,99 +641,155 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Review status</t>
+          <t>Workflow</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Draft — review pending</t>
+          <t>local</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Pages with extracted tables</t>
+          <t>Gemini model</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2 / 2</t>
+          <t>Not used</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Validation errors</t>
+          <t>Gemini request attempts</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Validation warnings</t>
+          <t>Gemini reported total tokens</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Rows with source evidence</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>21</v>
+          <t>Gemini interpretation</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>No external AI API requests.</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Review note</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
+          <t>Review status</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Draft — review pending</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Review completed (UTC)</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr"/>
+          <t>Pages with extracted tables</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>2 / 2</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
-        </is>
+          <t>Validation errors</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Validation warnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Rows with source evidence</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Review completed (UTC)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>OCR recognition scores are not measured extraction accuracy. Review all findings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Pages without extracted tables are explicitly flagged. No guarantee for arbitrary layouts.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B19"/>
+  <autoFilter ref="A1:B24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3061,7 +3117,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -3090,7 +3146,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3150,7 +3206,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.437923+00:00</t>
+          <t>2026-10-15T09:25:05.649860+00:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3168,7 +3224,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.441382+00:00</t>
+          <t>2026-10-15T09:25:05.655478+00:00</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -3188,7 +3244,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.571597+00:00</t>
+          <t>2026-10-15T09:25:05.776903+00:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -3208,7 +3264,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.572888+00:00</t>
+          <t>2026-10-15T09:25:05.778868+00:00</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -3228,7 +3284,7 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.703749+00:00</t>
+          <t>2026-10-15T09:25:05.909377+00:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -3248,7 +3304,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.703749+00:00</t>
+          <t>2026-10-15T09:25:05.909377+00:00</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -3266,7 +3322,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.711915+00:00</t>
+          <t>2026-10-15T09:25:05.912395+00:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3284,7 +3340,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15T08:42:34.714419+00:00</t>
+          <t>2026-10-15T09:25:05.916504+00:00</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
